--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 23:18</t>
+          <t>更新时间: 2026-09-13 23:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-13 23:43</t>
+          <t>更新时间: 2026-09-14 00:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 00:05</t>
+          <t>更新时间: 2026-09-14 07:36</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 07:36</t>
+          <t>更新时间: 2026-09-14 08:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 08:30</t>
+          <t>更新时间: 2026-09-14 09:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 09:15</t>
+          <t>更新时间: 2026-09-14 10:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 10:33</t>
+          <t>更新时间: 2026-09-14 12:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-14 12:08</t>
+          <t>更新时间: 2026-09-15 07:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 07:50</t>
+          <t>更新时间: 2026-09-15 08:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 08:31</t>
+          <t>更新时间: 2026-09-15 09:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 09:16</t>
+          <t>更新时间: 2026-09-15 10:35</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 10:35</t>
+          <t>更新时间: 2026-09-15 12:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-15 12:09</t>
+          <t>更新时间: 2026-09-16 07:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 07:49</t>
+          <t>更新时间: 2026-09-16 08:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 08:29</t>
+          <t>更新时间: 2026-09-16 09:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 09:14</t>
+          <t>更新时间: 2026-09-16 10:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 10:33</t>
+          <t>更新时间: 2026-09-16 17:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-16 17:01</t>
+          <t>更新时间: 2026-09-17 09:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 09:50</t>
+          <t>更新时间: 2026-09-17 12:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 12:47</t>
+          <t>更新时间: 2026-09-17 13:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 13:55</t>
+          <t>更新时间: 2026-09-17 15:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-17 15:48</t>
+          <t>更新时间: 2026-09-17 17:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 09:34</t>
+          <t>更新时间: 2026-09-18 12:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 12:37</t>
+          <t>更新时间: 2026-09-18 13:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 13:42</t>
+          <t>更新时间: 2026-09-18 15:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-18 16:42</t>
+          <t>更新时间: 2026-09-19 09:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 09:37</t>
+          <t>更新时间: 2026-09-19 12:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 12:32</t>
+          <t>更新时间: 2026-09-19 13:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 13:37</t>
+          <t>更新时间: 2026-09-19 15:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-19 16:29</t>
+          <t>更新时间: 2026-09-20 09:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 12:49</t>
+          <t>更新时间: 2026-09-20 13:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 13:55</t>
+          <t>更新时间: 2026-09-20 15:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 15:48</t>
+          <t>更新时间: 2026-09-20 17:01</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-20 17:01</t>
+          <t>更新时间: 2026-09-21 09:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 09:33</t>
+          <t>更新时间: 2026-09-21 12:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 12:49</t>
+          <t>更新时间: 2026-09-21 14:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 14:02</t>
+          <t>更新时间: 2026-09-21 16:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-21 16:02</t>
+          <t>更新时间: 2026-09-21 17:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 09:58</t>
+          <t>更新时间: 2026-09-22 12:48</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 12:48</t>
+          <t>更新时间: 2026-09-22 13:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 13:57</t>
+          <t>更新时间: 2026-09-22 15:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-22 16:59</t>
+          <t>更新时间: 2026-09-23 09:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 09:52</t>
+          <t>更新时间: 2026-09-23 12:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 12:40</t>
+          <t>更新时间: 2026-09-23 13:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 13:43</t>
+          <t>更新时间: 2026-09-23 15:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-23 15:50</t>
+          <t>更新时间: 2026-09-23 17:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 12:42</t>
+          <t>更新时间: 2026-09-24 13:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 13:58</t>
+          <t>更新时间: 2026-09-24 15:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 15:40</t>
+          <t>更新时间: 2026-09-24 16:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-24 16:58</t>
+          <t>更新时间: 2026-09-25 09:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 09:55</t>
+          <t>更新时间: 2026-09-25 12:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 12:52</t>
+          <t>更新时间: 2026-09-25 13:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 13:59</t>
+          <t>更新时间: 2026-09-25 15:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 15:58</t>
+          <t>更新时间: 2026-09-25 17:20</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-25 17:20</t>
+          <t>更新时间: 2026-09-26 10:00</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 10:00</t>
+          <t>更新时间: 2026-09-26 12:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 12:51</t>
+          <t>更新时间: 2026-09-26 13:59</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 13:59</t>
+          <t>更新时间: 2026-09-26 15:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-26 15:51</t>
+          <t>更新时间: 2026-09-26 17:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 13:13</t>
+          <t>更新时间: 2026-09-27 14:26</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 14:26</t>
+          <t>更新时间: 2026-09-27 16:21</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 16:21</t>
+          <t>更新时间: 2026-09-27 17:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-27 17:46</t>
+          <t>更新时间: 2026-09-28 10:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 13:17</t>
+          <t>更新时间: 2026-09-28 14:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 14:33</t>
+          <t>更新时间: 2026-09-28 16:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 16:47</t>
+          <t>更新时间: 2026-09-28 18:28</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-28 18:28</t>
+          <t>更新时间: 2026-09-29 10:55</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 10:55</t>
+          <t>更新时间: 2026-09-29 13:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 13:38</t>
+          <t>更新时间: 2026-09-29 14:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 14:42</t>
+          <t>更新时间: 2026-09-29 16:42</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 16:42</t>
+          <t>更新时间: 2026-09-29 18:22</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-29 18:22</t>
+          <t>更新时间: 2026-09-30 10:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 10:31</t>
+          <t>更新时间: 2026-09-30 13:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 13:27</t>
+          <t>更新时间: 2026-09-30 14:30</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 14:30</t>
+          <t>更新时间: 2026-09-30 16:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 16:43</t>
+          <t>更新时间: 2026-09-30 18:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-09-30 18:15</t>
+          <t>更新时间: 2026-10-01 10:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 10:32</t>
+          <t>更新时间: 2026-10-01 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 13:45</t>
+          <t>更新时间: 2026-10-01 15:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 15:03</t>
+          <t>更新时间: 2026-10-01 17:05</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 17:05</t>
+          <t>更新时间: 2026-10-01 18:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-01 18:41</t>
+          <t>更新时间: 2026-10-02 10:40</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 10:40</t>
+          <t>更新时间: 2026-10-02 13:29</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 13:29</t>
+          <t>更新时间: 2026-10-02 14:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 14:51</t>
+          <t>更新时间: 2026-10-02 16:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 16:39</t>
+          <t>更新时间: 2026-10-02 18:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-02 18:16</t>
+          <t>更新时间: 2026-10-03 10:27</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 10:27</t>
+          <t>更新时间: 2026-10-03 13:12</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 13:12</t>
+          <t>更新时间: 2026-10-03 14:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 14:16</t>
+          <t>更新时间: 2026-10-03 16:17</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 16:17</t>
+          <t>更新时间: 2026-10-03 17:38</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-03 17:38</t>
+          <t>更新时间: 2026-10-04 11:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 13:46</t>
+          <t>更新时间: 2026-10-04 14:41</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 14:41</t>
+          <t>更新时间: 2026-10-04 16:32</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 16:32</t>
+          <t>更新时间: 2026-10-04 18:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-04 18:23</t>
+          <t>更新时间: 2026-10-05 10:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 10:31</t>
+          <t>更新时间: 2026-10-05 13:31</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 13:31</t>
+          <t>更新时间: 2026-10-05 14:43</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 14:43</t>
+          <t>更新时间: 2026-10-05 17:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 17:14</t>
+          <t>更新时间: 2026-10-05 19:08</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-05 19:08</t>
+          <t>更新时间: 2026-10-06 11:24</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 11:24</t>
+          <t>更新时间: 2026-10-06 14:14</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 14:14</t>
+          <t>更新时间: 2026-10-06 15:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 15:23</t>
+          <t>更新时间: 2026-10-06 17:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-06 18:59</t>
+          <t>更新时间: 2026-10-07 10:50</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 10:50</t>
+          <t>更新时间: 2026-10-07 13:51</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 13:51</t>
+          <t>更新时间: 2026-10-07 15:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 15:02</t>
+          <t>更新时间: 2026-10-07 16:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 16:52</t>
+          <t>更新时间: 2026-10-07 18:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-07 18:49</t>
+          <t>更新时间: 2026-10-08 11:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 11:06</t>
+          <t>更新时间: 2026-10-08 13:56</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 13:56</t>
+          <t>更新时间: 2026-10-08 15:11</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 15:11</t>
+          <t>更新时间: 2026-10-08 17:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 17:09</t>
+          <t>更新时间: 2026-10-08 19:07</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-08 19:07</t>
+          <t>更新时间: 2026-10-09 11:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 11:23</t>
+          <t>更新时间: 2026-10-09 14:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 14:02</t>
+          <t>更新时间: 2026-10-09 15:15</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 15:15</t>
+          <t>更新时间: 2026-10-09 17:16</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 17:16</t>
+          <t>更新时间: 2026-10-09 19:06</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-09 19:06</t>
+          <t>更新时间: 2026-10-10 10:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 10:45</t>
+          <t>更新时间: 2026-10-10 13:45</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 13:45</t>
+          <t>更新时间: 2026-10-10 14:52</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 14:52</t>
+          <t>更新时间: 2026-10-10 16:39</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-10 16:39</t>
+          <t>更新时间: 2026-10-10 18:23</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 13:40</t>
+          <t>更新时间: 2026-10-11 14:57</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 14:57</t>
+          <t>更新时间: 2026-10-11 17:03</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 17:03</t>
+          <t>更新时间: 2026-10-11 18:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-11 18:33</t>
+          <t>更新时间: 2026-10-12 10:46</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 10:46</t>
+          <t>更新时间: 2026-10-12 13:49</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 13:49</t>
+          <t>更新时间: 2026-10-12 15:09</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 15:09</t>
+          <t>更新时间: 2026-10-12 17:25</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 17:25</t>
+          <t>更新时间: 2026-10-12 19:37</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-12 19:37</t>
+          <t>更新时间: 2026-10-13 12:02</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 14:43</t>
+          <t>更新时间: 2026-10-13 15:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-13 15:33</t>
+          <t>更新时间: 2026-10-13 17:33</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 12:47</t>
+          <t>更新时间: 2026-10-14 13:58</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 13:58</t>
+          <t>更新时间: 2026-10-14 15:47</t>
         </is>
       </c>
     </row>

--- a/reports/投递追踪表.xlsx
+++ b/reports/投递追踪表.xlsx
@@ -550,7 +550,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>更新时间: 2026-10-14 15:47</t>
+          <t>更新时间: 2026-10-14 17:15</t>
         </is>
       </c>
     </row>
